--- a/swift-crm-automation/Sample file/Input_data.xlsx
+++ b/swift-crm-automation/Sample file/Input_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New VI UAT PROJECT\WIP\Automation Folder\VI Demo 31.05.2026\VI Demo\swift-crm-automation\Sample file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B68B603-6735-4D5C-BFA1-3E356479DC95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC029B4-C944-439E-97A3-509D9D6F2C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{ABFECE7D-A40B-4DF2-B053-BF2EDF7965DD}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
   <si>
     <t>Username</t>
   </si>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>Sr. No.</t>
@@ -703,8 +700,7 @@
     <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="22.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -724,7 +720,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>5</v>
@@ -744,7 +740,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="7">
-        <v>9114667395</v>
+        <v>8399930232</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>10</v>
@@ -762,7 +758,7 @@
         <v>11</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -791,25 +787,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="22.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="C1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="G1" s="14" t="s">
         <v>18</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
@@ -820,19 +816,19 @@
         <v>199</v>
       </c>
       <c r="C2" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="E2" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="F2" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>23</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
@@ -843,19 +839,19 @@
         <v>149</v>
       </c>
       <c r="C3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="16" t="s">
+      <c r="F3" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="G3" s="18" t="s">
         <v>27</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
@@ -866,19 +862,19 @@
         <v>299</v>
       </c>
       <c r="C4" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>26</v>
-      </c>
       <c r="F4" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="18" t="s">
         <v>29</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
@@ -889,19 +885,19 @@
         <v>719</v>
       </c>
       <c r="C5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>26</v>
-      </c>
       <c r="F5" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="18" t="s">
         <v>31</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
@@ -912,19 +908,19 @@
         <v>369</v>
       </c>
       <c r="C6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="E6" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="16" t="s">
-        <v>22</v>
-      </c>
       <c r="F6" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="18" t="s">
         <v>33</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/swift-crm-automation/Sample file/Input_data.xlsx
+++ b/swift-crm-automation/Sample file/Input_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New VI UAT PROJECT\WIP\Automation Folder\VI Demo 31.05.2026\VI Demo\swift-crm-automation\Sample file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC029B4-C944-439E-97A3-509D9D6F2C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8CB1C1-9EF5-4D9D-B2CC-731E1FC6ABD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{ABFECE7D-A40B-4DF2-B053-BF2EDF7965DD}"/>
+    <workbookView xWindow="2640" yWindow="2640" windowWidth="15375" windowHeight="7785" xr2:uid="{ABFECE7D-A40B-4DF2-B053-BF2EDF7965DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Input excel" sheetId="1" r:id="rId1"/>
@@ -38,13 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
-  <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
   <si>
     <t>MSISDN</t>
   </si>
@@ -64,12 +58,6 @@
     <t>Vi App</t>
   </si>
   <si>
-    <t>COR4055772</t>
-  </si>
-  <si>
-    <t>Test@123456789!</t>
-  </si>
-  <si>
     <t>ODI</t>
   </si>
   <si>
@@ -143,6 +131,9 @@
   </si>
   <si>
     <t>Recharge</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -175,17 +166,14 @@
       <name val="Poppins"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Poppins"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Poppins"/>
     </font>
   </fonts>
@@ -227,7 +215,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -236,9 +224,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -256,17 +242,6 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -312,72 +287,65 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -690,83 +658,67 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3CD6BEF-943B-46C2-A3A0-9079289648AA}">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="25.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="25.42578125" defaultRowHeight="21.75" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="26.85546875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" style="15" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" style="15" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.140625" style="15" customWidth="1"/>
+    <col min="6" max="7" width="16.28515625" style="15" customWidth="1"/>
+    <col min="8" max="16384" width="25.42578125" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="22.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" s="18" customFormat="1" ht="22.5" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="22.5" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A2" s="2">
+        <v>8399930232</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="C2" s="4">
+        <v>149</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="22.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="7">
-        <v>8399930232</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="9">
-        <v>149</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>11</v>
+      <c r="F2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{033F518D-6B94-4A4D-8B91-E10659AB44F0}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -775,152 +727,152 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="19"/>
-    <col min="2" max="2" width="18.5703125" style="19" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="19" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" style="19" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="19"/>
-    <col min="6" max="6" width="26.7109375" style="19" customWidth="1"/>
-    <col min="7" max="7" width="68.140625" style="19" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="19"/>
+    <col min="1" max="1" width="9.140625" style="14"/>
+    <col min="2" max="2" width="18.5703125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="14" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" style="14" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="14"/>
+    <col min="6" max="6" width="26.7109375" style="14" customWidth="1"/>
+    <col min="7" max="7" width="68.140625" style="14" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="22.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="F1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="G1" s="9" t="s">
         <v>14</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="11">
         <v>199</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="13" t="s">
         <v>19</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="11">
         <v>149</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="16" t="s">
+      <c r="C3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>27</v>
+      <c r="D3" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="11">
         <v>299</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="16" t="s">
+      <c r="G4" s="13" t="s">
         <v>25</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15">
+      <c r="A5" s="10">
         <v>4</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="11">
         <v>719</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="16" t="s">
+      <c r="C5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>31</v>
+      <c r="D5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15">
+      <c r="A6" s="10">
         <v>5</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="11">
         <v>369</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>33</v>
+      <c r="C6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/swift-crm-automation/Sample file/Input_data.xlsx
+++ b/swift-crm-automation/Sample file/Input_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New VI UAT PROJECT\WIP\Automation Folder\VI Demo 31.05.2026\VI Demo\swift-crm-automation\Sample file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8CB1C1-9EF5-4D9D-B2CC-731E1FC6ABD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EFCF4B-6A5E-4E20-B1FF-1E7F7E1AB88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="15375" windowHeight="7785" xr2:uid="{ABFECE7D-A40B-4DF2-B053-BF2EDF7965DD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{ABFECE7D-A40B-4DF2-B053-BF2EDF7965DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Input excel" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
   <si>
     <t>MSISDN</t>
   </si>
@@ -58,9 +58,6 @@
     <t>Vi App</t>
   </si>
   <si>
-    <t>ODI</t>
-  </si>
-  <si>
     <t>Yes</t>
   </si>
   <si>
@@ -134,6 +131,15 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>RJ</t>
+  </si>
+  <si>
+    <t>RAJ</t>
+  </si>
+  <si>
+    <t>ASM</t>
   </si>
 </sst>
 </file>
@@ -290,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -344,6 +350,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -658,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3CD6BEF-943B-46C2-A3A0-9079289648AA}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultColWidth="25.42578125" defaultRowHeight="21.75" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="26.85546875" style="15" customWidth="1"/>
@@ -681,7 +694,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -695,26 +708,127 @@
     </row>
     <row r="2" spans="1:7" ht="22.5" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A2" s="2">
-        <v>8399930232</v>
+        <v>7374919937</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C2" s="4">
         <v>149</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="22.5" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A3" s="2">
+        <v>7374919937</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="4">
+        <v>149</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="22.5" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A4" s="2">
+        <v>98765</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="C4" s="4">
+        <v>149</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="22.5" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A5" s="2">
+        <v>8399930232</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="4">
+        <v>149</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="22.5" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A6" s="2">
+        <v>8399930232</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="4">
+        <v>149</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -739,25 +853,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="22.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="9" t="s">
         <v>13</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
@@ -768,19 +882,19 @@
         <v>199</v>
       </c>
       <c r="C2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="E2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="13" t="s">
         <v>18</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
@@ -791,19 +905,19 @@
         <v>149</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="11" t="s">
+      <c r="F3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="G3" s="13" t="s">
         <v>22</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
@@ -814,19 +928,19 @@
         <v>299</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>21</v>
-      </c>
       <c r="F4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="13" t="s">
         <v>24</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
@@ -837,19 +951,19 @@
         <v>719</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>21</v>
-      </c>
       <c r="F5" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="13" t="s">
         <v>26</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.3">
@@ -860,19 +974,19 @@
         <v>369</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>17</v>
-      </c>
       <c r="F6" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="13" t="s">
         <v>28</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
